--- a/artfynd/A 21482-2024 artfynd.xlsx
+++ b/artfynd/A 21482-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1810,6 +1810,238 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>120116719</v>
+      </c>
+      <c r="B12" t="n">
+        <v>97885</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>A 21482-2024, Varnö Ängsholmen, Srm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>693971</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6546941</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>08:44</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>08:47</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>120116594</v>
+      </c>
+      <c r="B13" t="n">
+        <v>97885</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>A 21482-2024, Varnö Ängsholmen, Srm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>693970</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6546944</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21482-2024 artfynd.xlsx
+++ b/artfynd/A 21482-2024 artfynd.xlsx
@@ -1812,7 +1812,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120116719</v>
+        <v>120116594</v>
       </c>
       <c r="B12" t="n">
         <v>97885</v>
@@ -1856,13 +1856,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>693971</v>
+        <v>693970</v>
       </c>
       <c r="R12" t="n">
-        <v>6546941</v>
+        <v>6546944</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1928,7 +1928,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120116594</v>
+        <v>120116719</v>
       </c>
       <c r="B13" t="n">
         <v>97885</v>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>693970</v>
+        <v>693971</v>
       </c>
       <c r="R13" t="n">
-        <v>6546944</v>
+        <v>6546941</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 21482-2024 artfynd.xlsx
+++ b/artfynd/A 21482-2024 artfynd.xlsx
@@ -1815,7 +1815,7 @@
         <v>120116594</v>
       </c>
       <c r="B12" t="n">
-        <v>97885</v>
+        <v>97908</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         <v>120116719</v>
       </c>
       <c r="B13" t="n">
-        <v>97885</v>
+        <v>97908</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 21482-2024 artfynd.xlsx
+++ b/artfynd/A 21482-2024 artfynd.xlsx
@@ -1812,7 +1812,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120116594</v>
+        <v>120116719</v>
       </c>
       <c r="B12" t="n">
         <v>97908</v>
@@ -1856,13 +1856,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>693970</v>
+        <v>693971</v>
       </c>
       <c r="R12" t="n">
-        <v>6546944</v>
+        <v>6546941</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1928,7 +1928,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120116719</v>
+        <v>120116594</v>
       </c>
       <c r="B13" t="n">
         <v>97908</v>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>693971</v>
+        <v>693970</v>
       </c>
       <c r="R13" t="n">
-        <v>6546941</v>
+        <v>6546944</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 21482-2024 artfynd.xlsx
+++ b/artfynd/A 21482-2024 artfynd.xlsx
@@ -1812,7 +1812,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120116719</v>
+        <v>120116594</v>
       </c>
       <c r="B12" t="n">
         <v>97908</v>
@@ -1856,13 +1856,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>693971</v>
+        <v>693970</v>
       </c>
       <c r="R12" t="n">
-        <v>6546941</v>
+        <v>6546944</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1928,7 +1928,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120116594</v>
+        <v>120116719</v>
       </c>
       <c r="B13" t="n">
         <v>97908</v>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>693970</v>
+        <v>693971</v>
       </c>
       <c r="R13" t="n">
-        <v>6546944</v>
+        <v>6546941</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AD13" t="b">
